--- a/UMGT/BOM/ECU BOM for 1 ECU complete.xlsx
+++ b/UMGT/BOM/ECU BOM for 1 ECU complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owen.maute\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0825CBFF-3FE7-44E2-A2AC-60CE7B81B6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960ECB74-97F7-4C0F-9B34-BC0E8FF681C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C838E9A-6698-40B3-8429-8704A2B50AFA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>PARTS LIST UMGT ECU</t>
   </si>
@@ -147,6 +147,12 @@
   </si>
   <si>
     <t>10CM-100CM Flat Flexible straight&amp;Up &amp; Down &amp; Left &amp; Right</t>
+  </si>
+  <si>
+    <t>100A current sensing for logic.</t>
+  </si>
+  <si>
+    <t>SSA-2-100A</t>
   </si>
 </sst>
 </file>
@@ -529,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C4891F-5E82-4F1F-8E50-577B3A5C6D0C}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
@@ -709,6 +715,20 @@
       </c>
       <c r="D13" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -724,6 +744,7 @@
     <hyperlink ref="C11" r:id="rId9" xr:uid="{F8358908-5F57-46F6-A8C3-0A1529F8069A}"/>
     <hyperlink ref="C12" r:id="rId10" xr:uid="{70BAF4BA-B2F2-4A06-9356-DB59457737AF}"/>
     <hyperlink ref="C13" r:id="rId11" xr:uid="{5EF81566-FDFA-46CD-8D28-B2AC67B4D228}"/>
+    <hyperlink ref="C14" r:id="rId12" xr:uid="{39810939-59D0-46FA-B7ED-53D56FADAC4D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
